--- a/CAPELCO_Dispatch_Input_Template.xlsx
+++ b/CAPELCO_Dispatch_Input_Template.xlsx
@@ -905,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>7.7807</v>
+        <v>19.7</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -915,7 +915,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Whole MW hourly; daily total &gt;=144 MWh</t>
+          <t>DG Plant Unit 1 (3.1 MW); one common DG Plant price; cost consolidated with DG2</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Peaking generator (0-or-full)</t>
+          <t>DG Plant Unit 2 (3.8 MW); one common DG Plant price; cost consolidated with DG1</t>
         </is>
       </c>
     </row>
